--- a/artfynd/A 18827-2025 artfynd.xlsx
+++ b/artfynd/A 18827-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>101555002</v>
       </c>
       <c r="B2" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613459.9260009683</v>
+        <v>613460</v>
       </c>
       <c r="R2" t="n">
-        <v>6966982.564996162</v>
+        <v>6966982</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2022-06-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,12 +783,7 @@
         <v>123301100</v>
       </c>
       <c r="B3" t="n">
-        <v>91714</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,12 +890,327 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Douglas Skarp</t>
+          <t>Douglas Skarp, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>101554965</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Laxsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>613367</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6967181</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>101554978</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Laxsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>613338</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6967237</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>101554973</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Laxsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>613358</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6967210</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 18827-2025 artfynd.xlsx
+++ b/artfynd/A 18827-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101555002</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301100</t>
         </is>
       </c>
     </row>
@@ -1003,6 +1018,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101554965</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101554978</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,8 +1238,20 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101554973</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>